--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="447">
   <si>
     <t>Id</t>
   </si>
@@ -1419,6 +1419,9 @@
   </si>
   <si>
     <t>WJBeta235</t>
+  </si>
+  <si>
+    <t>WJBeta236</t>
   </si>
 </sst>
 </file>
@@ -2503,7 +2506,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I231"/>
+  <dimension ref="A3:I232"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6600,7 +6603,24 @@
       <c r="F231" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G231" s="13"/>
+      <c r="G231" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="232" spans="3:7">
+      <c r="C232" s="4">
+        <v>236</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232" s="6">
+        <v>236</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G232" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="449">
   <si>
     <t>Id</t>
   </si>
@@ -1422,6 +1422,12 @@
   </si>
   <si>
     <t>WJBeta236</t>
+  </si>
+  <si>
+    <t>月光神域</t>
+  </si>
+  <si>
+    <t>WJBeta237</t>
   </si>
 </sst>
 </file>
@@ -2506,7 +2512,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I232"/>
+  <dimension ref="A3:I233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6620,7 +6626,24 @@
       <c r="F232" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="G232" s="13"/>
+      <c r="G232" s="13" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="233" spans="3:7">
+      <c r="C233" s="4">
+        <v>237</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" s="6">
+        <v>237</v>
+      </c>
+      <c r="F233" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="G233" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="450">
   <si>
     <t>Id</t>
   </si>
@@ -1428,6 +1428,9 @@
   </si>
   <si>
     <t>WJBeta237</t>
+  </si>
+  <si>
+    <t>霜火之巅</t>
   </si>
 </sst>
 </file>
@@ -2131,7 +2134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2164,6 +2167,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6643,7 +6647,9 @@
       <c r="F233" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="G233" s="13"/>
+      <c r="G233" s="20" t="s">
+        <v>449</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="451">
   <si>
     <t>Id</t>
   </si>
@@ -1431,6 +1431,9 @@
   </si>
   <si>
     <t>霜火之巅</t>
+  </si>
+  <si>
+    <t>WJBeta238</t>
   </si>
 </sst>
 </file>
@@ -2134,7 +2137,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2167,7 +2170,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2516,7 +2518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I233"/>
+  <dimension ref="A3:I234"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6647,8 +6649,25 @@
       <c r="F233" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="G233" s="20" t="s">
+      <c r="G233" s="13" t="s">
         <v>449</v>
+      </c>
+    </row>
+    <row r="234" spans="3:7">
+      <c r="C234" s="4">
+        <v>238</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" s="6">
+        <v>238</v>
+      </c>
+      <c r="F234" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G234" s="13" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="453">
   <si>
     <t>Id</t>
   </si>
@@ -1434,6 +1434,12 @@
   </si>
   <si>
     <t>WJBeta238</t>
+  </si>
+  <si>
+    <t>WJBeta239</t>
+  </si>
+  <si>
+    <t>翡翠之地</t>
   </si>
 </sst>
 </file>
@@ -2518,7 +2524,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I234"/>
+  <dimension ref="A3:I235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6670,6 +6676,23 @@
         <v>403</v>
       </c>
     </row>
+    <row r="235" spans="3:7">
+      <c r="C235" s="4">
+        <v>239</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" s="6">
+        <v>239</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G235" s="13" t="s">
+        <v>452</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="454">
   <si>
     <t>Id</t>
   </si>
@@ -1440,6 +1440,9 @@
   </si>
   <si>
     <t>翡翠之地</t>
+  </si>
+  <si>
+    <t>WJBeta240</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I235"/>
+  <dimension ref="A3:I236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6693,6 +6696,21 @@
         <v>452</v>
       </c>
     </row>
+    <row r="236" spans="3:7">
+      <c r="C236" s="4">
+        <v>240</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" s="6">
+        <v>240</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="G236" s="13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing20220362\Excel\StartConfig\Localhost\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\StartConfig\Localhost\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="455">
   <si>
     <t>Id</t>
   </si>
@@ -1443,6 +1443,9 @@
   </si>
   <si>
     <t>WJBeta240</t>
+  </si>
+  <si>
+    <t>青野拾光</t>
   </si>
 </sst>
 </file>
@@ -2146,7 +2149,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2179,6 +2182,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6709,7 +6713,9 @@
       <c r="F236" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="G236" s="13"/>
+      <c r="G236" s="20" t="s">
+        <v>454</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="456">
   <si>
     <t>Id</t>
   </si>
@@ -1446,6 +1446,9 @@
   </si>
   <si>
     <t>青野拾光</t>
+  </si>
+  <si>
+    <t>WJBeta241</t>
   </si>
 </sst>
 </file>
@@ -2149,7 +2152,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2182,7 +2185,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2531,7 +2533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I236"/>
+  <dimension ref="A3:I237"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6713,9 +6715,24 @@
       <c r="F236" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="G236" s="20" t="s">
+      <c r="G236" s="13" t="s">
         <v>454</v>
       </c>
+    </row>
+    <row r="237" spans="3:7">
+      <c r="C237" s="4">
+        <v>241</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" s="6">
+        <v>241</v>
+      </c>
+      <c r="F237" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="G237" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="457">
   <si>
     <t>Id</t>
   </si>
@@ -1449,6 +1449,9 @@
   </si>
   <si>
     <t>WJBeta241</t>
+  </si>
+  <si>
+    <t>逐光之路</t>
   </si>
 </sst>
 </file>
@@ -1651,12 +1654,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2152,7 +2155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2185,6 +2188,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6732,7 +6736,9 @@
       <c r="F237" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="G237" s="13"/>
+      <c r="G237" s="20" t="s">
+        <v>456</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="458">
   <si>
     <t>Id</t>
   </si>
@@ -1452,6 +1452,9 @@
   </si>
   <si>
     <t>逐光之路</t>
+  </si>
+  <si>
+    <t>WJBeta242</t>
   </si>
 </sst>
 </file>
@@ -1654,12 +1657,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2155,7 +2158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2188,7 +2191,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2537,7 +2539,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:I237"/>
+  <dimension ref="A3:I238"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
@@ -6736,9 +6738,24 @@
       <c r="F237" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="G237" s="20" t="s">
+      <c r="G237" s="13" t="s">
         <v>456</v>
       </c>
+    </row>
+    <row r="238" spans="3:7">
+      <c r="C238" s="4">
+        <v>242</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="6">
+        <v>242</v>
+      </c>
+      <c r="F238" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G238" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartZoneConfig@s.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="459">
   <si>
     <t>Id</t>
   </si>
@@ -1455,6 +1455,9 @@
   </si>
   <si>
     <t>WJBeta242</t>
+  </si>
+  <si>
+    <t>苍风之誓</t>
   </si>
 </sst>
 </file>
@@ -1657,12 +1660,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6755,7 +6758,9 @@
       <c r="F238" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="G238" s="13"/>
+      <c r="G238" s="13" t="s">
+        <v>458</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
